--- a/artfynd/A 23644-2026 artfynd.xlsx
+++ b/artfynd/A 23644-2026 artfynd.xlsx
@@ -3682,7 +3682,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134290983</v>
+        <v>134289942</v>
       </c>
       <c r="B31" t="n">
         <v>91960</v>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478870</v>
+        <v>478766</v>
       </c>
       <c r="R31" t="n">
-        <v>6954608</v>
+        <v>6954530</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3789,10 +3789,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134292410</v>
+        <v>134290983</v>
       </c>
       <c r="B32" t="n">
-        <v>83336</v>
+        <v>91960</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,21 +3800,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3824,10 +3824,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478799</v>
+        <v>478870</v>
       </c>
       <c r="R32" t="n">
-        <v>6954673</v>
+        <v>6954608</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134289942</v>
+        <v>134292410</v>
       </c>
       <c r="B33" t="n">
-        <v>91960</v>
+        <v>83336</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478766</v>
+        <v>478799</v>
       </c>
       <c r="R33" t="n">
-        <v>6954530</v>
+        <v>6954673</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4338,10 +4338,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134292560</v>
+        <v>134289390</v>
       </c>
       <c r="B37" t="n">
-        <v>57162</v>
+        <v>58658</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4349,27 +4349,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4378,13 +4378,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478745</v>
+        <v>478701</v>
       </c>
       <c r="R37" t="n">
-        <v>6954778</v>
+        <v>6954532</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4450,45 +4450,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134290699</v>
+        <v>134292560</v>
       </c>
       <c r="B38" t="n">
-        <v>79359</v>
+        <v>57162</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478820</v>
+        <v>478745</v>
       </c>
       <c r="R38" t="n">
-        <v>6954551</v>
+        <v>6954778</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4520,7 +4525,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4530,7 +4535,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4557,10 +4562,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134289590</v>
+        <v>134290699</v>
       </c>
       <c r="B39" t="n">
-        <v>83344</v>
+        <v>79359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4568,21 +4573,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,10 +4597,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478736</v>
+        <v>478820</v>
       </c>
       <c r="R39" t="n">
-        <v>6954521</v>
+        <v>6954551</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4627,7 +4632,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4637,7 +4642,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4664,53 +4669,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134289390</v>
+        <v>134289590</v>
       </c>
       <c r="B40" t="n">
-        <v>58658</v>
+        <v>83344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103044</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478701</v>
+        <v>478736</v>
       </c>
       <c r="R40" t="n">
-        <v>6954532</v>
+        <v>6954521</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4776,10 +4776,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134289781</v>
+        <v>134291930</v>
       </c>
       <c r="B41" t="n">
-        <v>79359</v>
+        <v>83208</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4787,21 +4787,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478759</v>
+        <v>478905</v>
       </c>
       <c r="R41" t="n">
-        <v>6954564</v>
+        <v>6954624</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4883,10 +4883,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134291930</v>
+        <v>134289781</v>
       </c>
       <c r="B42" t="n">
-        <v>83208</v>
+        <v>79359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478905</v>
+        <v>478759</v>
       </c>
       <c r="R42" t="n">
-        <v>6954624</v>
+        <v>6954564</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 23644-2026 artfynd.xlsx
+++ b/artfynd/A 23644-2026 artfynd.xlsx
@@ -2722,7 +2722,7 @@
         <v>134292693</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>134293043</v>
       </c>
       <c r="B23" t="n">
-        <v>80478</v>
+        <v>80485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>134292326</v>
       </c>
       <c r="B24" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>134290854</v>
       </c>
       <c r="B25" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>134292356</v>
       </c>
       <c r="B26" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>134291897</v>
       </c>
       <c r="B27" t="n">
-        <v>80478</v>
+        <v>80485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>134293003</v>
       </c>
       <c r="B28" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>134292992</v>
       </c>
       <c r="B29" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>134292079</v>
       </c>
       <c r="B30" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134289942</v>
+        <v>134292410</v>
       </c>
       <c r="B31" t="n">
-        <v>91960</v>
+        <v>83343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478766</v>
+        <v>478799</v>
       </c>
       <c r="R31" t="n">
-        <v>6954530</v>
+        <v>6954673</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3789,10 +3789,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134290983</v>
+        <v>134289942</v>
       </c>
       <c r="B32" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3824,10 +3824,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478870</v>
+        <v>478766</v>
       </c>
       <c r="R32" t="n">
-        <v>6954608</v>
+        <v>6954530</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3896,10 +3896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134292410</v>
+        <v>134290983</v>
       </c>
       <c r="B33" t="n">
-        <v>83336</v>
+        <v>91967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,21 +3907,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478799</v>
+        <v>478870</v>
       </c>
       <c r="R33" t="n">
-        <v>6954673</v>
+        <v>6954608</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4234,7 +4234,7 @@
         <v>134289417</v>
       </c>
       <c r="B36" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>134290699</v>
       </c>
       <c r="B39" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>134289590</v>
       </c>
       <c r="B40" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,10 +4776,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134291930</v>
+        <v>134289781</v>
       </c>
       <c r="B41" t="n">
-        <v>83208</v>
+        <v>79366</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4787,21 +4787,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478905</v>
+        <v>478759</v>
       </c>
       <c r="R41" t="n">
-        <v>6954624</v>
+        <v>6954564</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4883,10 +4883,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134289781</v>
+        <v>134291930</v>
       </c>
       <c r="B42" t="n">
-        <v>79359</v>
+        <v>83215</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478759</v>
+        <v>478905</v>
       </c>
       <c r="R42" t="n">
-        <v>6954564</v>
+        <v>6954624</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 23644-2026 artfynd.xlsx
+++ b/artfynd/A 23644-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122186172</v>
+        <v>122186158</v>
       </c>
       <c r="B2" t="n">
-        <v>97191</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478578</v>
+        <v>478725</v>
       </c>
       <c r="R2" t="n">
-        <v>6954850</v>
+        <v>6954813</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122186159</v>
+        <v>122186120</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478696</v>
+        <v>478740</v>
       </c>
       <c r="R3" t="n">
-        <v>6954735</v>
+        <v>6954715</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122186124</v>
+        <v>134292410</v>
       </c>
       <c r="B4" t="n">
-        <v>78301</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478680</v>
+        <v>478799</v>
       </c>
       <c r="R4" t="n">
-        <v>6954716</v>
+        <v>6954673</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +934,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122186174</v>
+        <v>122186124</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478635</v>
+        <v>478680</v>
       </c>
       <c r="R5" t="n">
-        <v>6954866</v>
+        <v>6954716</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,53 +1073,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122186169</v>
+        <v>134289942</v>
       </c>
       <c r="B6" t="n">
-        <v>94263</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2387</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478634</v>
+        <v>478766</v>
       </c>
       <c r="R6" t="n">
-        <v>6954832</v>
+        <v>6954530</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1138,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,27 +1168,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122186122</v>
+        <v>134290983</v>
       </c>
       <c r="B7" t="n">
-        <v>57812</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,37 +1191,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478702</v>
+        <v>478870</v>
       </c>
       <c r="R7" t="n">
-        <v>6954711</v>
+        <v>6954608</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1245,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,49 +1275,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122186125</v>
+        <v>122186121</v>
       </c>
       <c r="B8" t="n">
-        <v>56593</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478638</v>
+        <v>478749</v>
       </c>
       <c r="R8" t="n">
-        <v>6954681</v>
+        <v>6954722</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,15 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122186163</v>
+        <v>134291930</v>
       </c>
       <c r="B9" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,37 +1395,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478683</v>
+        <v>478905</v>
       </c>
       <c r="R9" t="n">
-        <v>6954796</v>
+        <v>6954624</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,12 +1449,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,27 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122186126</v>
+        <v>134292356</v>
       </c>
       <c r="B10" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,37 +1502,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478660</v>
+        <v>478824</v>
       </c>
       <c r="R10" t="n">
-        <v>6954631</v>
+        <v>6954660</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,12 +1556,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,27 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122186167</v>
+        <v>134293003</v>
       </c>
       <c r="B11" t="n">
-        <v>90857</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,37 +1609,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478634</v>
+        <v>478750</v>
       </c>
       <c r="R11" t="n">
-        <v>6954831</v>
+        <v>6954604</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,12 +1663,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,27 +1693,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186161</v>
+        <v>122186169</v>
       </c>
       <c r="B12" t="n">
-        <v>79765</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>2387</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478691</v>
+        <v>478634</v>
       </c>
       <c r="R12" t="n">
-        <v>6954785</v>
+        <v>6954832</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,53 +1802,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186120</v>
+        <v>134289417</v>
       </c>
       <c r="B13" t="n">
-        <v>74749</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478740</v>
+        <v>478703</v>
       </c>
       <c r="R13" t="n">
-        <v>6954715</v>
+        <v>6954523</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1867,12 +1867,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,65 +1897,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122186158</v>
+        <v>134289781</v>
       </c>
       <c r="B14" t="n">
-        <v>78690</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478725</v>
+        <v>478759</v>
       </c>
       <c r="R14" t="n">
-        <v>6954813</v>
+        <v>6954564</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1969,12 +1974,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1989,65 +2004,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122186166</v>
+        <v>134290699</v>
       </c>
       <c r="B15" t="n">
-        <v>97191</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478622</v>
+        <v>478820</v>
       </c>
       <c r="R15" t="n">
-        <v>6954830</v>
+        <v>6954551</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2071,12 +2081,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2091,65 +2111,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122186118</v>
+        <v>134292079</v>
       </c>
       <c r="B16" t="n">
-        <v>56593</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478548</v>
+        <v>478865</v>
       </c>
       <c r="R16" t="n">
-        <v>6954756</v>
+        <v>6954648</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2173,12 +2188,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,65 +2218,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122186123</v>
+        <v>134292693</v>
       </c>
       <c r="B17" t="n">
-        <v>97197</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478717</v>
+        <v>478762</v>
       </c>
       <c r="R17" t="n">
-        <v>6954740</v>
+        <v>6954626</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2275,12 +2295,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>21:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2295,69 +2325,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122186168</v>
+        <v>134289590</v>
       </c>
       <c r="B18" t="n">
-        <v>98141</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220093</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478632</v>
+        <v>478736</v>
       </c>
       <c r="R18" t="n">
-        <v>6954834</v>
+        <v>6954521</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2381,12 +2402,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2401,27 +2432,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122186165</v>
+        <v>122186119</v>
       </c>
       <c r="B19" t="n">
-        <v>57812</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,21 +2455,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103001</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2453,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478639</v>
+        <v>478528</v>
       </c>
       <c r="R19" t="n">
-        <v>6954772</v>
+        <v>6954781</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2515,37 +2541,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122186127</v>
+        <v>122186126</v>
       </c>
       <c r="B20" t="n">
-        <v>97191</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2555,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478642</v>
+        <v>478660</v>
       </c>
       <c r="R20" t="n">
-        <v>6954704</v>
+        <v>6954631</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2617,15 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122186121</v>
+        <v>134290854</v>
       </c>
       <c r="B21" t="n">
-        <v>82443</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,37 +2649,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478749</v>
+        <v>478868</v>
       </c>
       <c r="R21" t="n">
-        <v>6954722</v>
+        <v>6954569</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2687,12 +2703,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2707,22 +2733,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134292693</v>
+        <v>134292992</v>
       </c>
       <c r="B22" t="n">
-        <v>79366</v>
+        <v>80488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2754,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478762</v>
+        <v>478750</v>
       </c>
       <c r="R22" t="n">
-        <v>6954626</v>
+        <v>6954604</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,7 +2815,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2799,7 +2825,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2826,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134293043</v>
+        <v>122186161</v>
       </c>
       <c r="B23" t="n">
-        <v>80485</v>
+        <v>80460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,17 +2883,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478732</v>
+        <v>478691</v>
       </c>
       <c r="R23" t="n">
-        <v>6954607</v>
+        <v>6954785</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2891,22 +2917,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>21:34</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>21:34</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2921,22 +2937,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134292326</v>
+        <v>134291897</v>
       </c>
       <c r="B24" t="n">
-        <v>98053</v>
+        <v>80492</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2944,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478844</v>
+        <v>478902</v>
       </c>
       <c r="R24" t="n">
-        <v>6954653</v>
+        <v>6954624</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3003,7 +3019,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3013,7 +3029,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3040,32 +3056,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134290854</v>
+        <v>134293043</v>
       </c>
       <c r="B25" t="n">
-        <v>80481</v>
+        <v>80492</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3075,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478868</v>
+        <v>478732</v>
       </c>
       <c r="R25" t="n">
-        <v>6954569</v>
+        <v>6954607</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3110,7 +3126,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3120,7 +3136,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3147,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134292356</v>
+        <v>120789486</v>
       </c>
       <c r="B26" t="n">
-        <v>83215</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3158,37 +3174,53 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Rismyren, Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478824</v>
+        <v>478754</v>
       </c>
       <c r="R26" t="n">
-        <v>6954660</v>
+        <v>6954863</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3212,22 +3244,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3242,22 +3264,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134291897</v>
+        <v>122186118</v>
       </c>
       <c r="B27" t="n">
-        <v>80485</v>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,37 +3287,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478902</v>
+        <v>478548</v>
       </c>
       <c r="R27" t="n">
-        <v>6954624</v>
+        <v>6954756</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3319,22 +3341,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>20:42</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>20:42</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3349,60 +3361,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134293003</v>
+        <v>122186125</v>
       </c>
       <c r="B28" t="n">
-        <v>80482</v>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478750</v>
+        <v>478638</v>
       </c>
       <c r="R28" t="n">
-        <v>6954604</v>
+        <v>6954681</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3426,22 +3438,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>21:32</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>21:32</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3456,60 +3458,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134292992</v>
+        <v>122186159</v>
       </c>
       <c r="B29" t="n">
-        <v>80481</v>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478750</v>
+        <v>478696</v>
       </c>
       <c r="R29" t="n">
-        <v>6954604</v>
+        <v>6954735</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3533,22 +3535,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>21:32</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>21:32</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3563,57 +3555,62 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134292079</v>
+        <v>134292560</v>
       </c>
       <c r="B30" t="n">
-        <v>79366</v>
+        <v>57162</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478865</v>
+        <v>478745</v>
       </c>
       <c r="R30" t="n">
-        <v>6954648</v>
+        <v>6954778</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,7 +3642,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3655,7 +3652,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3682,45 +3679,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134292410</v>
+        <v>134292587</v>
       </c>
       <c r="B31" t="n">
-        <v>83343</v>
+        <v>5181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478799</v>
+        <v>478730</v>
       </c>
       <c r="R31" t="n">
-        <v>6954673</v>
+        <v>6954731</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3752,7 +3754,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3762,7 +3764,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3789,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134289942</v>
+        <v>122186122</v>
       </c>
       <c r="B32" t="n">
-        <v>91967</v>
+        <v>58388</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,37 +3802,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>103001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478766</v>
+        <v>478702</v>
       </c>
       <c r="R32" t="n">
-        <v>6954530</v>
+        <v>6954711</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3854,22 +3856,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>19:51</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>19:51</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3884,22 +3876,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134290983</v>
+        <v>122186165</v>
       </c>
       <c r="B33" t="n">
-        <v>91967</v>
+        <v>58388</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,37 +3899,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>103001</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478870</v>
+        <v>478639</v>
       </c>
       <c r="R33" t="n">
-        <v>6954608</v>
+        <v>6954772</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3961,22 +3953,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>20:17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>20:17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3991,65 +3973,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134292587</v>
+        <v>122186163</v>
       </c>
       <c r="B34" t="n">
-        <v>5181</v>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478730</v>
+        <v>478683</v>
       </c>
       <c r="R34" t="n">
-        <v>6954731</v>
+        <v>6954796</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4073,22 +4050,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>21:15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>21:15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4103,69 +4070,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134289905</v>
+        <v>122186174</v>
       </c>
       <c r="B35" t="n">
-        <v>58079</v>
+        <v>58114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478765</v>
+        <v>478635</v>
       </c>
       <c r="R35" t="n">
-        <v>6954554</v>
+        <v>6954866</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4189,22 +4147,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>19:45</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>19:45</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4219,22 +4167,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134289417</v>
+        <v>134289905</v>
       </c>
       <c r="B36" t="n">
-        <v>79366</v>
+        <v>58079</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4242,34 +4190,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478703</v>
+        <v>478765</v>
       </c>
       <c r="R36" t="n">
-        <v>6954523</v>
+        <v>6954554</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4301,7 +4258,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4311,7 +4268,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4450,10 +4407,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134292560</v>
+        <v>122186156</v>
       </c>
       <c r="B38" t="n">
-        <v>57162</v>
+        <v>99035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,42 +4418,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478745</v>
+        <v>478743</v>
       </c>
       <c r="R38" t="n">
-        <v>6954778</v>
+        <v>6954819</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4520,22 +4472,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>21:13</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>21:13</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4550,60 +4492,64 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134290699</v>
+        <v>122186168</v>
       </c>
       <c r="B39" t="n">
-        <v>79366</v>
+        <v>99022</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478820</v>
+        <v>478632</v>
       </c>
       <c r="R39" t="n">
-        <v>6954551</v>
+        <v>6954834</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4627,22 +4573,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>20:06</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>20:06</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4657,60 +4593,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134289590</v>
+        <v>122186123</v>
       </c>
       <c r="B40" t="n">
-        <v>83351</v>
+        <v>97989</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>221941</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478736</v>
+        <v>478717</v>
       </c>
       <c r="R40" t="n">
-        <v>6954521</v>
+        <v>6954740</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4734,22 +4670,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>19:33</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>19:33</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4764,60 +4690,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134289781</v>
+        <v>122186127</v>
       </c>
       <c r="B41" t="n">
-        <v>79366</v>
+        <v>97983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478759</v>
+        <v>478642</v>
       </c>
       <c r="R41" t="n">
-        <v>6954564</v>
+        <v>6954704</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4841,22 +4767,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>19:43</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>19:43</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4871,60 +4787,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134291930</v>
+        <v>122186166</v>
       </c>
       <c r="B42" t="n">
-        <v>83215</v>
+        <v>97983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478905</v>
+        <v>478622</v>
       </c>
       <c r="R42" t="n">
-        <v>6954624</v>
+        <v>6954830</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4948,22 +4864,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>20:44</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>20:44</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4978,15 +4884,219 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122186172</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>478578</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6954850</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134292326</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Rismyren, Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>478844</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6954653</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
           <t>Erik Wilhelmsson</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>Erik Wilhelmsson</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23644-2026 artfynd.xlsx
+++ b/artfynd/A 23644-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122186121</v>
+        <v>134701602</v>
       </c>
       <c r="B8" t="n">
-        <v>83173</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,37 +1298,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478749</v>
+        <v>478732</v>
       </c>
       <c r="R8" t="n">
-        <v>6954722</v>
+        <v>6954720</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,22 +1372,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134291930</v>
+        <v>134701754</v>
       </c>
       <c r="B9" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,21 +1395,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478905</v>
+        <v>478762</v>
       </c>
       <c r="R9" t="n">
-        <v>6954624</v>
+        <v>6954724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,22 +1449,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:44</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:44</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134292356</v>
+        <v>122186121</v>
       </c>
       <c r="B10" t="n">
-        <v>83222</v>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,17 +1512,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478824</v>
+        <v>478749</v>
       </c>
       <c r="R10" t="n">
-        <v>6954660</v>
+        <v>6954722</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1556,22 +1546,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,22 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134293003</v>
+        <v>134291930</v>
       </c>
       <c r="B11" t="n">
-        <v>80489</v>
+        <v>83222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478750</v>
+        <v>478905</v>
       </c>
       <c r="R11" t="n">
-        <v>6954604</v>
+        <v>6954624</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1648,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21:32</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1678,7 +1658,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>21:32</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,48 +1685,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186169</v>
+        <v>134292356</v>
       </c>
       <c r="B12" t="n">
-        <v>95962</v>
+        <v>83222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478634</v>
+        <v>478824</v>
       </c>
       <c r="R12" t="n">
-        <v>6954832</v>
+        <v>6954660</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,12 +1750,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,44 +1780,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134289417</v>
+        <v>134293003</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>80489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478703</v>
+        <v>478750</v>
       </c>
       <c r="R13" t="n">
-        <v>6954523</v>
+        <v>6954604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1872,7 +1862,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1882,7 +1872,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,48 +1899,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134289781</v>
+        <v>122186169</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>95962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478759</v>
+        <v>478634</v>
       </c>
       <c r="R14" t="n">
-        <v>6954564</v>
+        <v>6954832</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1974,22 +1964,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>19:43</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>19:43</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,19 +1984,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134290699</v>
+        <v>134289417</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2051,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478820</v>
+        <v>478703</v>
       </c>
       <c r="R15" t="n">
-        <v>6954551</v>
+        <v>6954523</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,7 +2066,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2096,7 +2076,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134292079</v>
+        <v>134289781</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2158,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478865</v>
+        <v>478759</v>
       </c>
       <c r="R16" t="n">
-        <v>6954648</v>
+        <v>6954564</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,7 +2173,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2203,7 +2183,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134292693</v>
+        <v>134290699</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2265,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478762</v>
+        <v>478820</v>
       </c>
       <c r="R17" t="n">
-        <v>6954626</v>
+        <v>6954551</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,7 +2280,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2310,7 +2290,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,32 +2317,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134289590</v>
+        <v>134292079</v>
       </c>
       <c r="B18" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478736</v>
+        <v>478865</v>
       </c>
       <c r="R18" t="n">
-        <v>6954521</v>
+        <v>6954648</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,7 +2387,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2417,7 +2397,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,48 +2424,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122186119</v>
+        <v>134292693</v>
       </c>
       <c r="B19" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478528</v>
+        <v>478762</v>
       </c>
       <c r="R19" t="n">
-        <v>6954781</v>
+        <v>6954626</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2509,12 +2489,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>21:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2529,60 +2519,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122186126</v>
+        <v>134700706</v>
       </c>
       <c r="B20" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478660</v>
+        <v>478577</v>
       </c>
       <c r="R20" t="n">
-        <v>6954631</v>
+        <v>6954733</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2606,12 +2596,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2626,44 +2616,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134290854</v>
+        <v>134703321</v>
       </c>
       <c r="B21" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478868</v>
+        <v>478615</v>
       </c>
       <c r="R21" t="n">
-        <v>6954569</v>
+        <v>6954640</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,22 +2693,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>20:12</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>20:12</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2745,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134292992</v>
+        <v>134289590</v>
       </c>
       <c r="B22" t="n">
-        <v>80488</v>
+        <v>83358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2756,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478750</v>
+        <v>478736</v>
       </c>
       <c r="R22" t="n">
-        <v>6954604</v>
+        <v>6954521</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,7 +2795,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:32</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2825,7 +2805,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>21:32</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,48 +2832,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122186161</v>
+        <v>134702117</v>
       </c>
       <c r="B23" t="n">
-        <v>80460</v>
+        <v>83358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478691</v>
+        <v>478747</v>
       </c>
       <c r="R23" t="n">
-        <v>6954785</v>
+        <v>6954700</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2917,12 +2897,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2937,60 +2917,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134291897</v>
+        <v>122186119</v>
       </c>
       <c r="B24" t="n">
-        <v>80492</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478902</v>
+        <v>478528</v>
       </c>
       <c r="R24" t="n">
-        <v>6954624</v>
+        <v>6954781</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3014,22 +2994,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>20:42</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>20:42</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3044,60 +3014,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134293043</v>
+        <v>122186126</v>
       </c>
       <c r="B25" t="n">
-        <v>80492</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rismyren, Rismyren, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478732</v>
+        <v>478660</v>
       </c>
       <c r="R25" t="n">
-        <v>6954607</v>
+        <v>6954631</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3121,22 +3091,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>21:34</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>21:34</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3151,22 +3111,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120789486</v>
+        <v>134290854</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>80488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,53 +3134,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rismyren, Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478754</v>
+        <v>478868</v>
       </c>
       <c r="R26" t="n">
-        <v>6954863</v>
+        <v>6954569</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3244,12 +3188,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3264,60 +3218,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122186118</v>
+        <v>134292992</v>
       </c>
       <c r="B27" t="n">
-        <v>57141</v>
+        <v>80488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478548</v>
+        <v>478750</v>
       </c>
       <c r="R27" t="n">
-        <v>6954756</v>
+        <v>6954604</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3341,12 +3295,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3361,60 +3325,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122186125</v>
+        <v>134703853</v>
       </c>
       <c r="B28" t="n">
-        <v>57141</v>
+        <v>80488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478638</v>
+        <v>478781</v>
       </c>
       <c r="R28" t="n">
-        <v>6954681</v>
+        <v>6954642</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3438,12 +3402,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3458,22 +3422,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122186159</v>
+        <v>122186161</v>
       </c>
       <c r="B29" t="n">
-        <v>57141</v>
+        <v>80460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3505,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478696</v>
+        <v>478691</v>
       </c>
       <c r="R29" t="n">
-        <v>6954735</v>
+        <v>6954785</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3567,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134292560</v>
+        <v>134291897</v>
       </c>
       <c r="B30" t="n">
-        <v>57162</v>
+        <v>80492</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,39 +3542,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478745</v>
+        <v>478902</v>
       </c>
       <c r="R30" t="n">
-        <v>6954778</v>
+        <v>6954624</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,7 +3601,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3652,7 +3611,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3679,10 +3638,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134292587</v>
+        <v>134293043</v>
       </c>
       <c r="B31" t="n">
-        <v>5181</v>
+        <v>80492</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3690,39 +3649,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478730</v>
+        <v>478732</v>
       </c>
       <c r="R31" t="n">
-        <v>6954731</v>
+        <v>6954607</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3754,7 +3708,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3764,7 +3718,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3791,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122186122</v>
+        <v>120789486</v>
       </c>
       <c r="B32" t="n">
-        <v>58388</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,37 +3756,53 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478702</v>
+        <v>478754</v>
       </c>
       <c r="R32" t="n">
-        <v>6954711</v>
+        <v>6954863</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3856,12 +3826,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3876,44 +3846,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122186165</v>
+        <v>122186118</v>
       </c>
       <c r="B33" t="n">
-        <v>58388</v>
+        <v>57141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103001</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3923,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478639</v>
+        <v>478548</v>
       </c>
       <c r="R33" t="n">
-        <v>6954772</v>
+        <v>6954756</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3985,32 +3955,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122186163</v>
+        <v>122186125</v>
       </c>
       <c r="B34" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,10 +3990,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478683</v>
+        <v>478638</v>
       </c>
       <c r="R34" t="n">
-        <v>6954796</v>
+        <v>6954681</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4082,32 +4052,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122186174</v>
+        <v>122186159</v>
       </c>
       <c r="B35" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4117,10 +4087,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478635</v>
+        <v>478696</v>
       </c>
       <c r="R35" t="n">
-        <v>6954866</v>
+        <v>6954735</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4179,42 +4149,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134289905</v>
+        <v>134292560</v>
       </c>
       <c r="B36" t="n">
-        <v>58079</v>
+        <v>57162</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4223,10 +4189,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478765</v>
+        <v>478745</v>
       </c>
       <c r="R36" t="n">
-        <v>6954554</v>
+        <v>6954778</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4258,7 +4224,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4268,7 +4234,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4295,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134289390</v>
+        <v>134292587</v>
       </c>
       <c r="B37" t="n">
-        <v>58658</v>
+        <v>5181</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4306,27 +4272,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103044</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4335,13 +4301,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478701</v>
+        <v>478730</v>
       </c>
       <c r="R37" t="n">
-        <v>6954532</v>
+        <v>6954731</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4370,7 +4336,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4380,7 +4346,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4407,10 +4373,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122186156</v>
+        <v>134700932</v>
       </c>
       <c r="B38" t="n">
-        <v>99035</v>
+        <v>5181</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4418,37 +4384,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478743</v>
+        <v>478656</v>
       </c>
       <c r="R38" t="n">
-        <v>6954819</v>
+        <v>6954795</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4472,12 +4438,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4492,61 +4458,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122186168</v>
+        <v>122186122</v>
       </c>
       <c r="B39" t="n">
-        <v>99022</v>
+        <v>58388</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220093</v>
+        <v>103001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478632</v>
+        <v>478702</v>
       </c>
       <c r="R39" t="n">
-        <v>6954834</v>
+        <v>6954711</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4605,32 +4567,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122186123</v>
+        <v>122186165</v>
       </c>
       <c r="B40" t="n">
-        <v>97989</v>
+        <v>58388</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221941</v>
+        <v>103001</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4640,10 +4602,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478717</v>
+        <v>478639</v>
       </c>
       <c r="R40" t="n">
-        <v>6954740</v>
+        <v>6954772</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4702,32 +4664,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122186127</v>
+        <v>122186163</v>
       </c>
       <c r="B41" t="n">
-        <v>97983</v>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4737,10 +4699,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478642</v>
+        <v>478683</v>
       </c>
       <c r="R41" t="n">
-        <v>6954704</v>
+        <v>6954796</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4799,32 +4761,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122186166</v>
+        <v>122186174</v>
       </c>
       <c r="B42" t="n">
-        <v>97983</v>
+        <v>58114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4834,10 +4796,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478622</v>
+        <v>478635</v>
       </c>
       <c r="R42" t="n">
-        <v>6954830</v>
+        <v>6954866</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4896,48 +4858,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122186172</v>
+        <v>134289905</v>
       </c>
       <c r="B43" t="n">
-        <v>97983</v>
+        <v>58079</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478578</v>
+        <v>478765</v>
       </c>
       <c r="R43" t="n">
-        <v>6954850</v>
+        <v>6954554</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4961,12 +4932,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4981,57 +4962,66 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134292326</v>
+        <v>134703831</v>
       </c>
       <c r="B44" t="n">
-        <v>98060</v>
+        <v>58079</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rismyren, Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478844</v>
+        <v>478780</v>
       </c>
       <c r="R44" t="n">
-        <v>6954653</v>
+        <v>6954638</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5058,22 +5048,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>20:56</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>20:56</t>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 4 stycken på samma ställe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5097,6 +5082,1102 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134289390</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Rismyren, Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>478701</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6954532</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134700578</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Rismyren, Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>478505</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6954736</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122186156</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>478743</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6954819</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122186168</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>478632</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6954834</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122186123</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>478717</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6954740</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122186127</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>478642</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6954704</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122186166</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>478622</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6954830</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122186172</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>478578</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6954850</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134292326</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Rismyren, Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>478844</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6954653</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134701774</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Rismyren, Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>478761</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6954724</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134704454</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Rismyren, Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>478646</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6954755</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23644-2026 artfynd.xlsx
+++ b/artfynd/A 23644-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186158</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186120</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134292410</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186124</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134289942</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134290983</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134701602</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134701754</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186121</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134291930</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134292356</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134293003</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186169</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134289417</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134289781</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2314,6 +2394,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134290699</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2421,6 +2506,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134292079</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2528,6 +2618,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134292693</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2625,6 +2720,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134700706</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2722,6 +2822,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703321</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2829,6 +2934,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134289590</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2926,6 +3036,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134702117</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3023,6 +3138,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186119</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186126</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3227,6 +3352,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134290854</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3334,6 +3464,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134292992</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3431,6 +3566,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703853</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3528,6 +3668,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186161</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3635,6 +3780,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134291897</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3742,6 +3892,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134293043</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3855,6 +4010,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120789486</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3952,6 +4112,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186118</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4049,6 +4214,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186125</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4146,6 +4316,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186159</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4258,6 +4433,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134292560</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4370,6 +4550,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134292587</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4467,6 +4652,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134700932</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4564,6 +4754,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186122</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4661,6 +4856,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186165</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4758,6 +4958,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186163</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4855,6 +5060,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186174</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4971,6 +5181,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134289905</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5082,6 +5297,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703831</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5194,6 +5414,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134289390</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5291,6 +5516,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134700578</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5388,6 +5618,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186156</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5489,6 +5724,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186168</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5586,6 +5826,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186123</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5683,6 +5928,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186127</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5780,6 +6030,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186166</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5877,6 +6132,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186172</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5984,6 +6244,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134292326</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6081,6 +6346,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134701774</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6178,8 +6448,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704454</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>